--- a/app/src/main/assets/methodmesh/odk_templates/svgselector/example_odk_showcase_svg_select.xlsx
+++ b/app/src/main/assets/methodmesh/odk_templates/svgselector/example_odk_showcase_svg_select.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R07026825634143d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R8e488bca98fc4eb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rf5740a5afb06409a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R74f96b1cc8a943a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R6b2d3ac358d64cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rc71c7d8784224daf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -336,15 +336,15 @@
       <x:c r="D2" s="8" t="str">
         <x:v>Select polygons on a stored SVG</x:v>
       </x:c>
-      <x:c r="E2" s="8" t="str"/>
-      <x:c r="F2" s="8" t="str"/>
-      <x:c r="G2" s="8" t="str"/>
-      <x:c r="H2" s="8" t="str"/>
-      <x:c r="I2" s="8" t="str"/>
-      <x:c r="J2" s="8" t="str"/>
-      <x:c r="K2" s="8" t="str"/>
-      <x:c r="L2" s="8" t="str"/>
-      <x:c r="M2" s="8" t="str"/>
+      <x:c r="E2" s="8"/>
+      <x:c r="F2" s="8"/>
+      <x:c r="G2" s="8"/>
+      <x:c r="H2" s="8"/>
+      <x:c r="I2" s="8"/>
+      <x:c r="J2" s="8"/>
+      <x:c r="K2" s="8"/>
+      <x:c r="L2" s="8"/>
+      <x:c r="M2" s="8"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="8" t="str">
@@ -362,15 +362,15 @@
       <x:c r="E3" s="8" t="str">
         <x:v>field-list</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str"/>
-      <x:c r="G3" s="8" t="str"/>
-      <x:c r="H3" s="8" t="str"/>
-      <x:c r="I3" s="8" t="str"/>
-      <x:c r="J3" s="8" t="str"/>
-      <x:c r="K3" s="8" t="str"/>
-      <x:c r="L3" s="8" t="str"/>
+      <x:c r="F3" s="8"/>
+      <x:c r="G3" s="8"/>
+      <x:c r="H3" s="8"/>
+      <x:c r="I3" s="8"/>
+      <x:c r="J3" s="8"/>
+      <x:c r="K3" s="8"/>
+      <x:c r="L3" s="8"/>
       <x:c r="M3" s="8" t="str">
-        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='svg.select',input_svg_name='bodymap_black.svg',input_selection_mode='sequence',return_mode='flat',input_payload_mode='FULL')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='svg.select',input_svg_name='bodymap_black.svg',input_selection_mode='heatmap',input_heatmap_levels='5',return_mode='flat',input_payload_mode='FULL')</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -381,20 +381,20 @@
         <x:v>native_interaction</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
-        <x:v>Complete the capability in MethodMesh, then Commit to return.</x:v>
+        <x:v>Tap the same polygon repeatedly to increase its heat level; then Commit to return.</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
-        <x:v>No undocumented ODK inputs have been invented for this showcase.</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="str"/>
-      <x:c r="F4" s="8" t="str"/>
-      <x:c r="G4" s="8" t="str"/>
-      <x:c r="H4" s="8" t="str"/>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str"/>
-      <x:c r="K4" s="8" t="str"/>
-      <x:c r="L4" s="8" t="str"/>
-      <x:c r="M4" s="8" t="str"/>
+        <x:v>Heat-map levels loop 0 → 1 → 2 → 3 → 4 → 5 → 0.</x:v>
+      </x:c>
+      <x:c r="E4" s="8"/>
+      <x:c r="F4" s="8"/>
+      <x:c r="G4" s="8"/>
+      <x:c r="H4" s="8"/>
+      <x:c r="I4" s="8"/>
+      <x:c r="J4" s="8"/>
+      <x:c r="K4" s="8"/>
+      <x:c r="L4" s="8"/>
+      <x:c r="M4" s="8"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="8" t="str">
@@ -412,16 +412,16 @@
       <x:c r="E5" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F5" s="8" t="str"/>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str"/>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
+      <x:c r="F5" s="8"/>
+      <x:c r="G5" s="8"/>
+      <x:c r="H5" s="8"/>
+      <x:c r="I5" s="8"/>
+      <x:c r="J5" s="8"/>
+      <x:c r="K5" s="8"/>
       <x:c r="L5" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M5" s="8" t="str"/>
+      <x:c r="M5" s="8"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="8" t="str">
@@ -439,16 +439,16 @@
       <x:c r="E6" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str"/>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
+      <x:c r="F6" s="8"/>
+      <x:c r="G6" s="8"/>
+      <x:c r="H6" s="8"/>
+      <x:c r="I6" s="8"/>
+      <x:c r="J6" s="8"/>
+      <x:c r="K6" s="8"/>
       <x:c r="L6" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M6" s="8" t="str"/>
+      <x:c r="M6" s="8"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="8" t="str">
@@ -466,16 +466,16 @@
       <x:c r="E7" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="str"/>
-      <x:c r="G7" s="8" t="str"/>
-      <x:c r="H7" s="8" t="str"/>
-      <x:c r="I7" s="8" t="str"/>
-      <x:c r="J7" s="8" t="str"/>
-      <x:c r="K7" s="8" t="str"/>
+      <x:c r="F7" s="8"/>
+      <x:c r="G7" s="8"/>
+      <x:c r="H7" s="8"/>
+      <x:c r="I7" s="8"/>
+      <x:c r="J7" s="8"/>
+      <x:c r="K7" s="8"/>
       <x:c r="L7" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M7" s="8" t="str"/>
+      <x:c r="M7" s="8"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="8" t="str">
@@ -488,196 +488,331 @@
         <x:v>Selected polygons</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Heat-map entries contain polygon_id and integer level.</x:v>
       </x:c>
       <x:c r="E8" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="str"/>
-      <x:c r="G8" s="8" t="str"/>
-      <x:c r="H8" s="8" t="str"/>
-      <x:c r="I8" s="8" t="str"/>
-      <x:c r="J8" s="8" t="str"/>
-      <x:c r="K8" s="8" t="str"/>
+      <x:c r="F8" s="8"/>
+      <x:c r="G8" s="8"/>
+      <x:c r="H8" s="8"/>
+      <x:c r="I8" s="8"/>
+      <x:c r="J8" s="8"/>
+      <x:c r="K8" s="8"/>
       <x:c r="L8" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M8" s="8" t="str"/>
+      <x:c r="M8" s="8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
-        <x:v>selection_events</x:v>
+        <x:v>selected_polygon_ids</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
-        <x:v>Selection events</x:v>
+        <x:v>Selected polygon IDs</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Convenience JSON array of selected polygon IDs.</x:v>
       </x:c>
       <x:c r="E9" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F9" s="8" t="str"/>
-      <x:c r="G9" s="8" t="str"/>
-      <x:c r="H9" s="8" t="str"/>
-      <x:c r="I9" s="8" t="str"/>
-      <x:c r="J9" s="8" t="str"/>
-      <x:c r="K9" s="8" t="str"/>
+      <x:c r="F9" s="8"/>
+      <x:c r="G9" s="8"/>
+      <x:c r="H9" s="8"/>
+      <x:c r="I9" s="8"/>
+      <x:c r="J9" s="8"/>
+      <x:c r="K9" s="8"/>
       <x:c r="L9" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M9" s="8" t="str"/>
+      <x:c r="M9" s="8"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>selection_audit_hash</x:v>
+        <x:v>selected_count</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>Selection audit hash</x:v>
+        <x:v>Selected polygon count</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Count of selected/non-zero polygons.</x:v>
       </x:c>
       <x:c r="E10" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F10" s="8" t="str"/>
-      <x:c r="G10" s="8" t="str"/>
-      <x:c r="H10" s="8" t="str"/>
-      <x:c r="I10" s="8" t="str"/>
-      <x:c r="J10" s="8" t="str"/>
-      <x:c r="K10" s="8" t="str"/>
+      <x:c r="F10" s="8"/>
+      <x:c r="G10" s="8"/>
+      <x:c r="H10" s="8"/>
+      <x:c r="I10" s="8"/>
+      <x:c r="J10" s="8"/>
+      <x:c r="K10" s="8"/>
       <x:c r="L10" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M10" s="8" t="str"/>
+      <x:c r="M10" s="8"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
-        <x:v>selection_started_at</x:v>
+        <x:v>selection_summary</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>Selection started</x:v>
+        <x:v>Selection summary</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Human-readable selection projection returned by MethodMesh.</x:v>
       </x:c>
       <x:c r="E11" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F11" s="8" t="str"/>
-      <x:c r="G11" s="8" t="str"/>
-      <x:c r="H11" s="8" t="str"/>
-      <x:c r="I11" s="8" t="str"/>
-      <x:c r="J11" s="8" t="str"/>
-      <x:c r="K11" s="8" t="str"/>
+      <x:c r="F11" s="8"/>
+      <x:c r="G11" s="8"/>
+      <x:c r="H11" s="8"/>
+      <x:c r="I11" s="8"/>
+      <x:c r="J11" s="8"/>
+      <x:c r="K11" s="8"/>
       <x:c r="L11" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M11" s="8" t="str"/>
+      <x:c r="M11" s="8"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>selection_completed_at</x:v>
+        <x:v>polygon_levels</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>Selection completed</x:v>
+        <x:v>Polygon heat levels</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Polygon ID to integer heat level mapping returned by MethodMesh.</x:v>
       </x:c>
       <x:c r="E12" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F12" s="8" t="str"/>
-      <x:c r="G12" s="8" t="str"/>
-      <x:c r="H12" s="8" t="str"/>
-      <x:c r="I12" s="8" t="str"/>
-      <x:c r="J12" s="8" t="str"/>
-      <x:c r="K12" s="8" t="str"/>
+      <x:c r="F12" s="8"/>
+      <x:c r="G12" s="8"/>
+      <x:c r="H12" s="8"/>
+      <x:c r="I12" s="8"/>
+      <x:c r="J12" s="8"/>
+      <x:c r="K12" s="8"/>
       <x:c r="L12" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M12" s="8" t="str"/>
+      <x:c r="M12" s="8"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
-        <x:v>methodmesh_full_json</x:v>
+        <x:v>heatmap_max_level</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
-        <x:v>Methodmesh Full Json</x:v>
+        <x:v>Heat-map maximum level</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
-        <x:v>Shared MethodMesh FULL execution envelope. Retained for complete execution/audit capture; capability-specific return fields are projected separately.</x:v>
+        <x:v>Configured maximum non-zero heat level returned by MethodMesh.</x:v>
       </x:c>
       <x:c r="E13" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F13" s="8" t="str"/>
-      <x:c r="G13" s="8" t="str"/>
-      <x:c r="H13" s="8" t="str"/>
-      <x:c r="I13" s="8" t="str"/>
-      <x:c r="J13" s="8" t="str"/>
-      <x:c r="K13" s="8" t="str"/>
+      <x:c r="F13" s="8"/>
+      <x:c r="G13" s="8"/>
+      <x:c r="H13" s="8"/>
+      <x:c r="I13" s="8"/>
+      <x:c r="J13" s="8"/>
+      <x:c r="K13" s="8"/>
       <x:c r="L13" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M13" s="8" t="str"/>
+      <x:c r="M13" s="8"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="8" t="str">
-        <x:v>end_group</x:v>
-      </x:c>
-      <x:c r="B14" s="8" t="str"/>
-      <x:c r="C14" s="8" t="str"/>
-      <x:c r="D14" s="8" t="str"/>
-      <x:c r="E14" s="8" t="str"/>
-      <x:c r="F14" s="8" t="str"/>
-      <x:c r="G14" s="8" t="str"/>
-      <x:c r="H14" s="8" t="str"/>
-      <x:c r="I14" s="8" t="str"/>
-      <x:c r="J14" s="8" t="str"/>
-      <x:c r="K14" s="8" t="str"/>
-      <x:c r="L14" s="8" t="str"/>
-      <x:c r="M14" s="8" t="str"/>
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="str">
+        <x:v>selection_events</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="str">
+        <x:v>Selection events</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="str">
+        <x:v>Timestamped selection and heat-level events returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F14" s="8"/>
+      <x:c r="G14" s="8"/>
+      <x:c r="H14" s="8"/>
+      <x:c r="I14" s="8"/>
+      <x:c r="J14" s="8"/>
+      <x:c r="K14" s="8"/>
+      <x:c r="L14" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M14" s="8"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="8" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="str">
+        <x:v>selection_audit_hash</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="str">
+        <x:v>Selection audit hash</x:v>
+      </x:c>
+      <x:c r="D15" s="8" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F15" s="8"/>
+      <x:c r="G15" s="8"/>
+      <x:c r="H15" s="8"/>
+      <x:c r="I15" s="8"/>
+      <x:c r="J15" s="8"/>
+      <x:c r="K15" s="8"/>
+      <x:c r="L15" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M15" s="8"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>selection_started_at</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Selection started</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>selection_completed_at</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Selection completed</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Returned by MethodMesh.</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+      <x:c r="I17"/>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>methodmesh_full_json</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Methodmesh Full Json</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Shared MethodMesh FULL execution envelope. Retained for complete execution/audit capture; capability-specific return fields are projected separately.</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+      <x:c r="I18"/>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
+      <x:c r="L18" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="M18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>end_group</x:v>
+      </x:c>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+      <x:c r="I19"/>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
+      <x:c r="M19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
         <x:v>note</x:v>
       </x:c>
-      <x:c r="B15" s="8" t="str">
+      <x:c r="B20" t="str">
         <x:v>return_summary</x:v>
       </x:c>
-      <x:c r="C15" s="8" t="str">
-        <x:v>MethodMesh return captured. Status: ${methodmesh_status}</x:v>
-      </x:c>
-      <x:c r="D15" s="8" t="str">
-        <x:v>Only fields relevant to this capability are stored, plus the shared FULL envelope.</x:v>
-      </x:c>
-      <x:c r="E15" s="8" t="str"/>
-      <x:c r="F15" s="8" t="str"/>
-      <x:c r="G15" s="8" t="str"/>
-      <x:c r="H15" s="8" t="str"/>
-      <x:c r="I15" s="8" t="str"/>
-      <x:c r="J15" s="8" t="str"/>
-      <x:c r="K15" s="8" t="str"/>
-      <x:c r="L15" s="8" t="str"/>
-      <x:c r="M15" s="8" t="str"/>
+      <x:c r="C20" t="str">
+        <x:v>MethodMesh return captured. ${selection_summary}</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>Heat-map levels are available in polygon_levels; the shared FULL envelope is retained for audit/provenance.</x:v>
+      </x:c>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
+      <x:c r="M20"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -737,7 +872,7 @@
         <x:v>svgselector_svg_select</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>2026090701</x:v>
+        <x:v>2026091302</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
